--- a/AAII_Financials/Quarterly/FLGZY_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/FLGZY_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="383" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="423" uniqueCount="92">
   <si>
     <t>FLGZY</t>
   </si>
@@ -656,83 +656,91 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:Q102"/>
+  <dimension ref="A5:S102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:19" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E7" s="2">
+        <v>46112</v>
+      </c>
+      <c r="F7" s="2">
         <v>46022</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45930</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>45838</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>45747</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>45657</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>45565</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>45473</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>45382</v>
       </c>
-      <c r="L7" s="2">
+      <c r="N7" s="2">
         <v>45291</v>
       </c>
-      <c r="M7" s="2">
+      <c r="O7" s="2">
         <v>45199</v>
       </c>
-      <c r="N7" s="2">
+      <c r="P7" s="2">
         <v>45107</v>
       </c>
-      <c r="O7" s="2">
+      <c r="Q7" s="2">
         <v>45016</v>
       </c>
-      <c r="P7" s="2">
+      <c r="R7" s="2">
         <v>44926</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="S7" s="2">
         <v>44834</v>
       </c>
     </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
@@ -778,8 +786,14 @@
       <c r="Q8" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R8" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S8" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="9" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -825,8 +839,14 @@
       <c r="Q9" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R9" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S9" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -872,8 +892,14 @@
       <c r="Q10" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R10" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S10" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -891,8 +917,10 @@
       <c r="O11" s="3"/>
       <c r="P11" s="3"/>
       <c r="Q11" s="3"/>
-    </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R11" s="3"/>
+      <c r="S11" s="3"/>
+    </row>
+    <row r="12" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -938,8 +966,14 @@
       <c r="Q12" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R12" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S12" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -985,8 +1019,14 @@
       <c r="Q13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R13" s="3">
+        <v>0</v>
+      </c>
+      <c r="S13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1032,8 +1072,14 @@
       <c r="Q14" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S14" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="15" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1079,8 +1125,14 @@
       <c r="Q15" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R15" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S15" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="16" spans="1:19" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1095,8 +1147,10 @@
       <c r="O16" s="3"/>
       <c r="P16" s="3"/>
       <c r="Q16" s="3"/>
-    </row>
-    <row r="17" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R16" s="3"/>
+      <c r="S16" s="3"/>
+    </row>
+    <row r="17" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
@@ -1142,8 +1196,14 @@
       <c r="Q17" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="18" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R17" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S17" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="18" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
@@ -1189,8 +1249,14 @@
       <c r="Q18" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="19" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R18" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S18" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="19" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1208,8 +1274,10 @@
       <c r="O19" s="3"/>
       <c r="P19" s="3"/>
       <c r="Q19" s="3"/>
-    </row>
-    <row r="20" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R19" s="3"/>
+      <c r="S19" s="3"/>
+    </row>
+    <row r="20" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1255,8 +1323,14 @@
       <c r="Q20" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="21" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S20" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="21" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -1302,8 +1376,14 @@
       <c r="Q21" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="22" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R21" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S21" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="22" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1349,8 +1429,14 @@
       <c r="Q22" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="23" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R22" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S22" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="23" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
@@ -1396,8 +1482,14 @@
       <c r="Q23" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="24" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R23" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S23" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="24" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1443,8 +1535,14 @@
       <c r="Q24" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="25" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R24" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S24" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="25" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1490,8 +1588,14 @@
       <c r="Q25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R25" s="3">
+        <v>0</v>
+      </c>
+      <c r="S25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
@@ -1537,8 +1641,14 @@
       <c r="Q26" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="27" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R26" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S26" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="27" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
@@ -1584,8 +1694,14 @@
       <c r="Q27" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="28" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R27" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S27" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="28" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1631,8 +1747,14 @@
       <c r="Q28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R28" s="3">
+        <v>0</v>
+      </c>
+      <c r="S28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1678,8 +1800,14 @@
       <c r="Q29" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="30" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R29" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S29" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="30" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1725,8 +1853,14 @@
       <c r="Q30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R30" s="3">
+        <v>0</v>
+      </c>
+      <c r="S30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1772,8 +1906,14 @@
       <c r="Q31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R31" s="3">
+        <v>0</v>
+      </c>
+      <c r="S31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -1819,8 +1959,14 @@
       <c r="Q32" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="33" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S32" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="33" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
@@ -1866,8 +2012,14 @@
       <c r="Q33" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="34" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R33" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S33" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="34" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1913,8 +2065,14 @@
       <c r="Q34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R34" s="3">
+        <v>0</v>
+      </c>
+      <c r="S34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
@@ -1960,60 +2118,72 @@
       <c r="Q35" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="37" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R35" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S35" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="37" spans="2:19" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E38" s="2">
+        <v>46112</v>
+      </c>
+      <c r="F38" s="2">
         <v>46022</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45930</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>45838</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>45747</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>45657</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>45565</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>45473</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>45382</v>
       </c>
-      <c r="L38" s="2">
+      <c r="N38" s="2">
         <v>45291</v>
       </c>
-      <c r="M38" s="2">
+      <c r="O38" s="2">
         <v>45199</v>
       </c>
-      <c r="N38" s="2">
+      <c r="P38" s="2">
         <v>45107</v>
       </c>
-      <c r="O38" s="2">
+      <c r="Q38" s="2">
         <v>45016</v>
       </c>
-      <c r="P38" s="2">
+      <c r="R38" s="2">
         <v>44926</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="S38" s="2">
         <v>44834</v>
       </c>
     </row>
-    <row r="39" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2031,8 +2201,10 @@
       <c r="O39" s="3"/>
       <c r="P39" s="3"/>
       <c r="Q39" s="3"/>
-    </row>
-    <row r="40" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R39" s="3"/>
+      <c r="S39" s="3"/>
+    </row>
+    <row r="40" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2050,431 +2222,487 @@
       <c r="O40" s="3"/>
       <c r="P40" s="3"/>
       <c r="Q40" s="3"/>
-    </row>
-    <row r="41" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R40" s="3"/>
+      <c r="S40" s="3"/>
+    </row>
+    <row r="41" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>244800</v>
+      </c>
+      <c r="E41" s="3">
+        <v>246600</v>
+      </c>
+      <c r="F41" s="3">
         <v>201300</v>
       </c>
-      <c r="E41" s="3">
+      <c r="G41" s="3">
         <v>200200</v>
       </c>
-      <c r="F41" s="3">
+      <c r="H41" s="3">
         <v>323000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="I41" s="3">
         <v>290600</v>
       </c>
-      <c r="H41" s="3">
+      <c r="J41" s="3">
         <v>356700</v>
       </c>
-      <c r="I41" s="3">
+      <c r="K41" s="3">
         <v>382600</v>
       </c>
-      <c r="J41" s="3">
+      <c r="L41" s="3">
         <v>258600</v>
       </c>
-      <c r="K41" s="3">
+      <c r="M41" s="3">
         <v>257600</v>
       </c>
-      <c r="L41" s="3">
+      <c r="N41" s="3">
         <v>356700</v>
       </c>
-      <c r="M41" s="3">
+      <c r="O41" s="3">
         <v>328500</v>
       </c>
-      <c r="N41" s="3">
+      <c r="P41" s="3">
         <v>271900</v>
       </c>
-      <c r="O41" s="3">
+      <c r="Q41" s="3">
         <v>266600</v>
       </c>
-      <c r="P41" s="3">
+      <c r="R41" s="3">
         <v>282500</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="S41" s="3">
         <v>266100</v>
       </c>
     </row>
-    <row r="42" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>85800</v>
+      </c>
+      <c r="E42" s="3">
+        <v>86400</v>
+      </c>
+      <c r="F42" s="3">
         <v>331200</v>
       </c>
-      <c r="E42" s="3">
+      <c r="G42" s="3">
         <v>329300</v>
       </c>
-      <c r="F42" s="3">
+      <c r="H42" s="3">
         <v>29900</v>
       </c>
-      <c r="G42" s="3">
+      <c r="I42" s="3">
         <v>26900</v>
       </c>
-      <c r="H42" s="3">
+      <c r="J42" s="3">
         <v>43600</v>
       </c>
-      <c r="I42" s="3">
+      <c r="K42" s="3">
         <v>46800</v>
       </c>
-      <c r="J42" s="3">
+      <c r="L42" s="3">
         <v>51100</v>
       </c>
-      <c r="K42" s="3">
+      <c r="M42" s="3">
         <v>50900</v>
       </c>
-      <c r="L42" s="3">
+      <c r="N42" s="3">
         <v>358100</v>
       </c>
-      <c r="M42" s="3">
+      <c r="O42" s="3">
         <v>329700</v>
       </c>
-      <c r="N42" s="3">
+      <c r="P42" s="3">
         <v>209400</v>
       </c>
-      <c r="O42" s="3">
+      <c r="Q42" s="3">
         <v>205300</v>
       </c>
-      <c r="P42" s="3">
+      <c r="R42" s="3">
         <v>498800</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="S42" s="3">
         <v>469900</v>
       </c>
     </row>
-    <row r="43" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>367100</v>
+      </c>
+      <c r="E43" s="3">
+        <v>369800</v>
+      </c>
+      <c r="F43" s="3">
         <v>232200</v>
       </c>
-      <c r="E43" s="3">
+      <c r="G43" s="3">
         <v>230900</v>
       </c>
-      <c r="F43" s="3">
+      <c r="H43" s="3">
         <v>385900</v>
       </c>
-      <c r="G43" s="3">
+      <c r="I43" s="3">
         <v>347200</v>
       </c>
-      <c r="H43" s="3">
+      <c r="J43" s="3">
         <v>185400</v>
       </c>
-      <c r="I43" s="3">
+      <c r="K43" s="3">
         <v>198900</v>
       </c>
-      <c r="J43" s="3">
+      <c r="L43" s="3">
         <v>381900</v>
       </c>
-      <c r="K43" s="3">
+      <c r="M43" s="3">
         <v>380500</v>
       </c>
-      <c r="L43" s="3">
+      <c r="N43" s="3">
         <v>227100</v>
       </c>
-      <c r="M43" s="3">
+      <c r="O43" s="3">
         <v>209100</v>
       </c>
-      <c r="N43" s="3">
+      <c r="P43" s="3">
         <v>367100</v>
       </c>
-      <c r="O43" s="3">
+      <c r="Q43" s="3">
         <v>360000</v>
       </c>
-      <c r="P43" s="3">
+      <c r="R43" s="3">
         <v>191400</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="S43" s="3">
         <v>180300</v>
       </c>
     </row>
-    <row r="44" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>19200</v>
+      </c>
+      <c r="E44" s="3">
+        <v>19300</v>
+      </c>
+      <c r="F44" s="3">
         <v>19800</v>
       </c>
-      <c r="E44" s="3">
+      <c r="G44" s="3">
         <v>19700</v>
       </c>
-      <c r="F44" s="3">
+      <c r="H44" s="3">
         <v>22600</v>
       </c>
-      <c r="G44" s="3">
+      <c r="I44" s="3">
         <v>20400</v>
       </c>
-      <c r="H44" s="3">
+      <c r="J44" s="3">
         <v>21000</v>
       </c>
-      <c r="I44" s="3">
+      <c r="K44" s="3">
         <v>22500</v>
       </c>
-      <c r="J44" s="3">
+      <c r="L44" s="3">
         <v>22300</v>
       </c>
-      <c r="K44" s="3">
+      <c r="M44" s="3">
         <v>22200</v>
       </c>
-      <c r="L44" s="3">
+      <c r="N44" s="3">
         <v>23400</v>
       </c>
-      <c r="M44" s="3">
+      <c r="O44" s="3">
         <v>21500</v>
       </c>
-      <c r="N44" s="3">
+      <c r="P44" s="3">
         <v>21500</v>
       </c>
-      <c r="O44" s="3">
+      <c r="Q44" s="3">
         <v>21000</v>
       </c>
-      <c r="P44" s="3">
+      <c r="R44" s="3">
         <v>11800</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="S44" s="3">
         <v>11100</v>
       </c>
     </row>
-    <row r="45" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>45500</v>
+      </c>
+      <c r="E45" s="3">
+        <v>45900</v>
+      </c>
+      <c r="F45" s="3">
         <v>47500</v>
       </c>
-      <c r="E45" s="3">
+      <c r="G45" s="3">
         <v>47300</v>
       </c>
-      <c r="F45" s="3">
+      <c r="H45" s="3">
         <v>30200</v>
       </c>
-      <c r="G45" s="3">
+      <c r="I45" s="3">
         <v>27200</v>
       </c>
-      <c r="H45" s="3">
+      <c r="J45" s="3">
         <v>38500</v>
       </c>
-      <c r="I45" s="3">
+      <c r="K45" s="3">
         <v>41300</v>
       </c>
-      <c r="J45" s="3">
+      <c r="L45" s="3">
         <v>29500</v>
       </c>
-      <c r="K45" s="3">
+      <c r="M45" s="3">
         <v>29400</v>
       </c>
-      <c r="L45" s="3">
+      <c r="N45" s="3">
         <v>35000</v>
       </c>
-      <c r="M45" s="3">
+      <c r="O45" s="3">
         <v>32300</v>
       </c>
-      <c r="N45" s="3">
+      <c r="P45" s="3">
         <v>28900</v>
       </c>
-      <c r="O45" s="3">
+      <c r="Q45" s="3">
         <v>28400</v>
       </c>
-      <c r="P45" s="3">
+      <c r="R45" s="3">
         <v>62300</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="S45" s="3">
         <v>58700</v>
       </c>
     </row>
-    <row r="46" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>762400</v>
+      </c>
+      <c r="E46" s="3">
+        <v>768000</v>
+      </c>
+      <c r="F46" s="3">
         <v>960500</v>
       </c>
-      <c r="E46" s="3">
+      <c r="G46" s="3">
         <v>955100</v>
       </c>
-      <c r="F46" s="3">
+      <c r="H46" s="3">
         <v>791700</v>
       </c>
-      <c r="G46" s="3">
+      <c r="I46" s="3">
         <v>712300</v>
       </c>
-      <c r="H46" s="3">
+      <c r="J46" s="3">
         <v>815500</v>
       </c>
-      <c r="I46" s="3">
+      <c r="K46" s="3">
         <v>874900</v>
       </c>
-      <c r="J46" s="3">
+      <c r="L46" s="3">
         <v>743400</v>
       </c>
-      <c r="K46" s="3">
+      <c r="M46" s="3">
         <v>740500</v>
       </c>
-      <c r="L46" s="3">
+      <c r="N46" s="3">
         <v>1143100</v>
       </c>
-      <c r="M46" s="3">
+      <c r="O46" s="3">
         <v>1052600</v>
       </c>
-      <c r="N46" s="3">
+      <c r="P46" s="3">
         <v>898800</v>
       </c>
-      <c r="O46" s="3">
+      <c r="Q46" s="3">
         <v>881300</v>
       </c>
-      <c r="P46" s="3">
+      <c r="R46" s="3">
         <v>1184600</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="S46" s="3">
         <v>1116100</v>
       </c>
     </row>
-    <row r="47" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>318400</v>
+      </c>
+      <c r="E47" s="3">
+        <v>320800</v>
+      </c>
+      <c r="F47" s="3">
         <v>356500</v>
       </c>
-      <c r="E47" s="3">
+      <c r="G47" s="3">
         <v>354500</v>
       </c>
-      <c r="F47" s="3">
+      <c r="H47" s="3">
         <v>382500</v>
       </c>
-      <c r="G47" s="3">
+      <c r="I47" s="3">
         <v>344100</v>
       </c>
-      <c r="H47" s="3">
+      <c r="J47" s="3">
         <v>315600</v>
       </c>
-      <c r="I47" s="3">
+      <c r="K47" s="3">
         <v>338600</v>
       </c>
-      <c r="J47" s="3">
+      <c r="L47" s="3">
         <v>297200</v>
       </c>
-      <c r="K47" s="3">
+      <c r="M47" s="3">
         <v>296100</v>
       </c>
-      <c r="L47" s="3">
+      <c r="N47" s="3">
         <v>282900</v>
       </c>
-      <c r="M47" s="3">
+      <c r="O47" s="3">
         <v>260500</v>
       </c>
-      <c r="N47" s="3">
+      <c r="P47" s="3">
         <v>309000</v>
       </c>
-      <c r="O47" s="3">
+      <c r="Q47" s="3">
         <v>303000</v>
       </c>
-      <c r="P47" s="3">
+      <c r="R47" s="3">
         <v>334200</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="S47" s="3">
         <v>314800</v>
       </c>
     </row>
-    <row r="48" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>4520700</v>
+      </c>
+      <c r="E48" s="3">
+        <v>4553800</v>
+      </c>
+      <c r="F48" s="3">
         <v>4339100</v>
       </c>
-      <c r="E48" s="3">
+      <c r="G48" s="3">
         <v>4315000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="H48" s="3">
         <v>4151100</v>
       </c>
-      <c r="G48" s="3">
+      <c r="I48" s="3">
         <v>3734700</v>
       </c>
-      <c r="H48" s="3">
+      <c r="J48" s="3">
         <v>3564600</v>
       </c>
-      <c r="I48" s="3">
+      <c r="K48" s="3">
         <v>3824000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="L48" s="3">
         <v>3426700</v>
       </c>
-      <c r="K48" s="3">
+      <c r="M48" s="3">
         <v>3413600</v>
       </c>
-      <c r="L48" s="3">
+      <c r="N48" s="3">
         <v>3533600</v>
       </c>
-      <c r="M48" s="3">
+      <c r="O48" s="3">
         <v>3253700</v>
       </c>
-      <c r="N48" s="3">
+      <c r="P48" s="3">
         <v>3224300</v>
       </c>
-      <c r="O48" s="3">
+      <c r="Q48" s="3">
         <v>3161600</v>
       </c>
-      <c r="P48" s="3">
+      <c r="R48" s="3">
         <v>3086500</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="S48" s="3">
         <v>2908000</v>
       </c>
     </row>
-    <row r="49" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>505300</v>
+      </c>
+      <c r="E49" s="3">
+        <v>509000</v>
+      </c>
+      <c r="F49" s="3">
         <v>487900</v>
       </c>
-      <c r="E49" s="3">
+      <c r="G49" s="3">
         <v>485200</v>
       </c>
-      <c r="F49" s="3">
+      <c r="H49" s="3">
         <v>492900</v>
       </c>
-      <c r="G49" s="3">
+      <c r="I49" s="3">
         <v>443500</v>
       </c>
-      <c r="H49" s="3">
+      <c r="J49" s="3">
         <v>441300</v>
       </c>
-      <c r="I49" s="3">
+      <c r="K49" s="3">
         <v>473400</v>
       </c>
-      <c r="J49" s="3">
+      <c r="L49" s="3">
         <v>462300</v>
       </c>
-      <c r="K49" s="3">
+      <c r="M49" s="3">
         <v>460500</v>
       </c>
-      <c r="L49" s="3">
+      <c r="N49" s="3">
         <v>414200</v>
       </c>
-      <c r="M49" s="3">
+      <c r="O49" s="3">
         <v>381400</v>
       </c>
-      <c r="N49" s="3">
+      <c r="P49" s="3">
         <v>419100</v>
       </c>
-      <c r="O49" s="3">
+      <c r="Q49" s="3">
         <v>410900</v>
       </c>
-      <c r="P49" s="3">
+      <c r="R49" s="3">
         <v>378300</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="S49" s="3">
         <v>356400</v>
       </c>
     </row>
-    <row r="50" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2520,8 +2748,14 @@
       <c r="Q50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R50" s="3">
+        <v>0</v>
+      </c>
+      <c r="S50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2567,55 +2801,67 @@
       <c r="Q51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R51" s="3">
+        <v>0</v>
+      </c>
+      <c r="S51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>815700</v>
+      </c>
+      <c r="E52" s="3">
+        <v>821700</v>
+      </c>
+      <c r="F52" s="3">
         <v>882700</v>
       </c>
-      <c r="E52" s="3">
+      <c r="G52" s="3">
         <v>877700</v>
       </c>
-      <c r="F52" s="3">
+      <c r="H52" s="3">
         <v>862100</v>
       </c>
-      <c r="G52" s="3">
+      <c r="I52" s="3">
         <v>775600</v>
       </c>
-      <c r="H52" s="3">
+      <c r="J52" s="3">
         <v>599200</v>
       </c>
-      <c r="I52" s="3">
+      <c r="K52" s="3">
         <v>642800</v>
       </c>
-      <c r="J52" s="3">
+      <c r="L52" s="3">
         <v>616600</v>
       </c>
-      <c r="K52" s="3">
+      <c r="M52" s="3">
         <v>614300</v>
       </c>
-      <c r="L52" s="3">
+      <c r="N52" s="3">
         <v>681300</v>
       </c>
-      <c r="M52" s="3">
+      <c r="O52" s="3">
         <v>627300</v>
       </c>
-      <c r="N52" s="3">
+      <c r="P52" s="3">
         <v>655300</v>
       </c>
-      <c r="O52" s="3">
+      <c r="Q52" s="3">
         <v>642500</v>
       </c>
-      <c r="P52" s="3">
+      <c r="R52" s="3">
         <v>648300</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="S52" s="3">
         <v>610800</v>
       </c>
     </row>
-    <row r="53" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2661,55 +2907,67 @@
       <c r="Q53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R53" s="3">
+        <v>0</v>
+      </c>
+      <c r="S53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>6925100</v>
+      </c>
+      <c r="E54" s="3">
+        <v>6975900</v>
+      </c>
+      <c r="F54" s="3">
         <v>7028600</v>
       </c>
-      <c r="E54" s="3">
+      <c r="G54" s="3">
         <v>6989500</v>
       </c>
-      <c r="F54" s="3">
+      <c r="H54" s="3">
         <v>6684600</v>
       </c>
-      <c r="G54" s="3">
+      <c r="I54" s="3">
         <v>6014000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="J54" s="3">
         <v>5741100</v>
       </c>
-      <c r="I54" s="3">
+      <c r="K54" s="3">
         <v>6158900</v>
       </c>
-      <c r="J54" s="3">
+      <c r="L54" s="3">
         <v>5551200</v>
       </c>
-      <c r="K54" s="3">
+      <c r="M54" s="3">
         <v>5530000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="N54" s="3">
         <v>6063600</v>
       </c>
-      <c r="M54" s="3">
+      <c r="O54" s="3">
         <v>5583300</v>
       </c>
-      <c r="N54" s="3">
+      <c r="P54" s="3">
         <v>5513000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="Q54" s="3">
         <v>5405800</v>
       </c>
-      <c r="P54" s="3">
+      <c r="R54" s="3">
         <v>5640700</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="S54" s="3">
         <v>5314400</v>
       </c>
     </row>
-    <row r="55" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2727,8 +2985,10 @@
       <c r="O55" s="3"/>
       <c r="P55" s="3"/>
       <c r="Q55" s="3"/>
-    </row>
-    <row r="56" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R55" s="3"/>
+      <c r="S55" s="3"/>
+    </row>
+    <row r="56" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2746,290 +3006,328 @@
       <c r="O56" s="3"/>
       <c r="P56" s="3"/>
       <c r="Q56" s="3"/>
-    </row>
-    <row r="57" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R56" s="3"/>
+      <c r="S56" s="3"/>
+    </row>
+    <row r="57" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>100600</v>
+      </c>
+      <c r="E57" s="3">
+        <v>101400</v>
+      </c>
+      <c r="F57" s="3">
         <v>90500</v>
       </c>
-      <c r="E57" s="3">
+      <c r="G57" s="3">
         <v>90000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="H57" s="3">
         <v>88400</v>
       </c>
-      <c r="G57" s="3">
+      <c r="I57" s="3">
         <v>79500</v>
       </c>
-      <c r="H57" s="3">
+      <c r="J57" s="3">
         <v>70000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="K57" s="3">
         <v>75100</v>
       </c>
-      <c r="J57" s="3">
+      <c r="L57" s="3">
         <v>67300</v>
       </c>
-      <c r="K57" s="3">
+      <c r="M57" s="3">
         <v>67100</v>
       </c>
-      <c r="L57" s="3">
+      <c r="N57" s="3">
         <v>62300</v>
       </c>
-      <c r="M57" s="3">
+      <c r="O57" s="3">
         <v>57400</v>
       </c>
-      <c r="N57" s="3">
+      <c r="P57" s="3">
         <v>63500</v>
       </c>
-      <c r="O57" s="3">
+      <c r="Q57" s="3">
         <v>62200</v>
       </c>
-      <c r="P57" s="3">
+      <c r="R57" s="3">
         <v>48000</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="S57" s="3">
         <v>45200</v>
       </c>
     </row>
-    <row r="58" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>38700</v>
+      </c>
+      <c r="E58" s="3">
+        <v>39000</v>
+      </c>
+      <c r="F58" s="3">
         <v>31400</v>
       </c>
-      <c r="E58" s="3">
+      <c r="G58" s="3">
         <v>31200</v>
       </c>
-      <c r="F58" s="3">
+      <c r="H58" s="3">
         <v>29500</v>
       </c>
-      <c r="G58" s="3">
+      <c r="I58" s="3">
         <v>26600</v>
       </c>
-      <c r="H58" s="3">
+      <c r="J58" s="3">
         <v>29700</v>
       </c>
-      <c r="I58" s="3">
+      <c r="K58" s="3">
         <v>31800</v>
       </c>
-      <c r="J58" s="3">
+      <c r="L58" s="3">
         <v>96300</v>
       </c>
-      <c r="K58" s="3">
+      <c r="M58" s="3">
         <v>95900</v>
       </c>
-      <c r="L58" s="3">
+      <c r="N58" s="3">
         <v>388900</v>
       </c>
-      <c r="M58" s="3">
+      <c r="O58" s="3">
         <v>358100</v>
       </c>
-      <c r="N58" s="3">
+      <c r="P58" s="3">
         <v>362000</v>
       </c>
-      <c r="O58" s="3">
+      <c r="Q58" s="3">
         <v>354900</v>
       </c>
-      <c r="P58" s="3">
+      <c r="R58" s="3">
         <v>455700</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="S58" s="3">
         <v>429400</v>
       </c>
     </row>
-    <row r="59" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>361900</v>
+      </c>
+      <c r="E59" s="3">
+        <v>364500</v>
+      </c>
+      <c r="F59" s="3">
         <v>313900</v>
       </c>
-      <c r="E59" s="3">
+      <c r="G59" s="3">
         <v>312100</v>
       </c>
-      <c r="F59" s="3">
+      <c r="H59" s="3">
         <v>296400</v>
       </c>
-      <c r="G59" s="3">
+      <c r="I59" s="3">
         <v>266600</v>
       </c>
-      <c r="H59" s="3">
+      <c r="J59" s="3">
         <v>265200</v>
       </c>
-      <c r="I59" s="3">
+      <c r="K59" s="3">
         <v>284500</v>
       </c>
-      <c r="J59" s="3">
+      <c r="L59" s="3">
         <v>247100</v>
       </c>
-      <c r="K59" s="3">
+      <c r="M59" s="3">
         <v>246100</v>
       </c>
-      <c r="L59" s="3">
+      <c r="N59" s="3">
         <v>256200</v>
       </c>
-      <c r="M59" s="3">
+      <c r="O59" s="3">
         <v>235900</v>
       </c>
-      <c r="N59" s="3">
+      <c r="P59" s="3">
         <v>283100</v>
       </c>
-      <c r="O59" s="3">
+      <c r="Q59" s="3">
         <v>277600</v>
       </c>
-      <c r="P59" s="3">
+      <c r="R59" s="3">
         <v>198300</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="S59" s="3">
         <v>186900</v>
       </c>
     </row>
-    <row r="60" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>501200</v>
+      </c>
+      <c r="E60" s="3">
+        <v>504900</v>
+      </c>
+      <c r="F60" s="3">
         <v>448600</v>
       </c>
-      <c r="E60" s="3">
+      <c r="G60" s="3">
         <v>446100</v>
       </c>
-      <c r="F60" s="3">
+      <c r="H60" s="3">
         <v>414300</v>
       </c>
-      <c r="G60" s="3">
+      <c r="I60" s="3">
         <v>372800</v>
       </c>
-      <c r="H60" s="3">
+      <c r="J60" s="3">
         <v>373800</v>
       </c>
-      <c r="I60" s="3">
+      <c r="K60" s="3">
         <v>401000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="L60" s="3">
         <v>410600</v>
       </c>
-      <c r="K60" s="3">
+      <c r="M60" s="3">
         <v>409100</v>
       </c>
-      <c r="L60" s="3">
+      <c r="N60" s="3">
         <v>719900</v>
       </c>
-      <c r="M60" s="3">
+      <c r="O60" s="3">
         <v>662900</v>
       </c>
-      <c r="N60" s="3">
+      <c r="P60" s="3">
         <v>708500</v>
       </c>
-      <c r="O60" s="3">
+      <c r="Q60" s="3">
         <v>694700</v>
       </c>
-      <c r="P60" s="3">
+      <c r="R60" s="3">
         <v>715300</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="S60" s="3">
         <v>673900</v>
       </c>
     </row>
-    <row r="61" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>2180100</v>
+      </c>
+      <c r="E61" s="3">
+        <v>2196100</v>
+      </c>
+      <c r="F61" s="3">
         <v>2103300</v>
       </c>
-      <c r="E61" s="3">
+      <c r="G61" s="3">
         <v>2091600</v>
       </c>
-      <c r="F61" s="3">
+      <c r="H61" s="3">
         <v>2052900</v>
       </c>
-      <c r="G61" s="3">
+      <c r="I61" s="3">
         <v>1846900</v>
       </c>
-      <c r="H61" s="3">
+      <c r="J61" s="3">
         <v>1603400</v>
       </c>
-      <c r="I61" s="3">
+      <c r="K61" s="3">
         <v>1720100</v>
       </c>
-      <c r="J61" s="3">
+      <c r="L61" s="3">
         <v>1510700</v>
       </c>
-      <c r="K61" s="3">
+      <c r="M61" s="3">
         <v>1504900</v>
       </c>
-      <c r="L61" s="3">
+      <c r="N61" s="3">
         <v>1470900</v>
       </c>
-      <c r="M61" s="3">
+      <c r="O61" s="3">
         <v>1354400</v>
       </c>
-      <c r="N61" s="3">
+      <c r="P61" s="3">
         <v>1356600</v>
       </c>
-      <c r="O61" s="3">
+      <c r="Q61" s="3">
         <v>1330200</v>
       </c>
-      <c r="P61" s="3">
+      <c r="R61" s="3">
         <v>1615700</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="S61" s="3">
         <v>1522300</v>
       </c>
     </row>
-    <row r="62" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>332700</v>
+      </c>
+      <c r="E62" s="3">
+        <v>335100</v>
+      </c>
+      <c r="F62" s="3">
         <v>349700</v>
       </c>
-      <c r="E62" s="3">
+      <c r="G62" s="3">
         <v>347800</v>
       </c>
-      <c r="F62" s="3">
+      <c r="H62" s="3">
         <v>357900</v>
       </c>
-      <c r="G62" s="3">
+      <c r="I62" s="3">
         <v>322000</v>
       </c>
-      <c r="H62" s="3">
+      <c r="J62" s="3">
         <v>324300</v>
       </c>
-      <c r="I62" s="3">
+      <c r="K62" s="3">
         <v>347900</v>
       </c>
-      <c r="J62" s="3">
+      <c r="L62" s="3">
         <v>332000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="M62" s="3">
         <v>330700</v>
       </c>
-      <c r="L62" s="3">
+      <c r="N62" s="3">
         <v>346800</v>
       </c>
-      <c r="M62" s="3">
+      <c r="O62" s="3">
         <v>319300</v>
       </c>
-      <c r="N62" s="3">
+      <c r="P62" s="3">
         <v>324700</v>
       </c>
-      <c r="O62" s="3">
+      <c r="Q62" s="3">
         <v>318400</v>
       </c>
-      <c r="P62" s="3">
+      <c r="R62" s="3">
         <v>323700</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="S62" s="3">
         <v>305000</v>
       </c>
     </row>
-    <row r="63" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3075,8 +3373,14 @@
       <c r="Q63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R63" s="3">
+        <v>0</v>
+      </c>
+      <c r="S63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3122,8 +3426,14 @@
       <c r="Q64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R64" s="3">
+        <v>0</v>
+      </c>
+      <c r="S64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3169,55 +3479,67 @@
       <c r="Q65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R65" s="3">
+        <v>0</v>
+      </c>
+      <c r="S65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>3163500</v>
+      </c>
+      <c r="E66" s="3">
+        <v>3186700</v>
+      </c>
+      <c r="F66" s="3">
         <v>3057300</v>
       </c>
-      <c r="E66" s="3">
+      <c r="G66" s="3">
         <v>3040300</v>
       </c>
-      <c r="F66" s="3">
+      <c r="H66" s="3">
         <v>2979800</v>
       </c>
-      <c r="G66" s="3">
+      <c r="I66" s="3">
         <v>2680900</v>
       </c>
-      <c r="H66" s="3">
+      <c r="J66" s="3">
         <v>2467600</v>
       </c>
-      <c r="I66" s="3">
+      <c r="K66" s="3">
         <v>2647200</v>
       </c>
-      <c r="J66" s="3">
+      <c r="L66" s="3">
         <v>2396400</v>
       </c>
-      <c r="K66" s="3">
+      <c r="M66" s="3">
         <v>2387200</v>
       </c>
-      <c r="L66" s="3">
+      <c r="N66" s="3">
         <v>2734100</v>
       </c>
-      <c r="M66" s="3">
+      <c r="O66" s="3">
         <v>2517600</v>
       </c>
-      <c r="N66" s="3">
+      <c r="P66" s="3">
         <v>2488900</v>
       </c>
-      <c r="O66" s="3">
+      <c r="Q66" s="3">
         <v>2440400</v>
       </c>
-      <c r="P66" s="3">
+      <c r="R66" s="3">
         <v>2743400</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="S66" s="3">
         <v>2584700</v>
       </c>
     </row>
-    <row r="67" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3235,8 +3557,10 @@
       <c r="O67" s="3"/>
       <c r="P67" s="3"/>
       <c r="Q67" s="3"/>
-    </row>
-    <row r="68" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R67" s="3"/>
+      <c r="S67" s="3"/>
+    </row>
+    <row r="68" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3282,8 +3606,14 @@
       <c r="Q68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R68" s="3">
+        <v>0</v>
+      </c>
+      <c r="S68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3329,8 +3659,14 @@
       <c r="Q69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R69" s="3">
+        <v>0</v>
+      </c>
+      <c r="S69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3376,8 +3712,14 @@
       <c r="Q70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R70" s="3">
+        <v>0</v>
+      </c>
+      <c r="S70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3423,55 +3765,67 @@
       <c r="Q71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R71" s="3">
+        <v>0</v>
+      </c>
+      <c r="S71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>3513400</v>
+      </c>
+      <c r="E72" s="3">
+        <v>3539100</v>
+      </c>
+      <c r="F72" s="3">
         <v>3727600</v>
       </c>
-      <c r="E72" s="3">
+      <c r="G72" s="3">
         <v>3706900</v>
       </c>
-      <c r="F72" s="3">
+      <c r="H72" s="3">
         <v>3449500</v>
       </c>
-      <c r="G72" s="3">
+      <c r="I72" s="3">
         <v>3103500</v>
       </c>
-      <c r="H72" s="3">
+      <c r="J72" s="3">
         <v>2967500</v>
       </c>
-      <c r="I72" s="3">
+      <c r="K72" s="3">
         <v>3183500</v>
       </c>
-      <c r="J72" s="3">
+      <c r="L72" s="3">
         <v>2820400</v>
       </c>
-      <c r="K72" s="3">
+      <c r="M72" s="3">
         <v>2809600</v>
       </c>
-      <c r="L72" s="3">
+      <c r="N72" s="3">
         <v>2927200</v>
       </c>
-      <c r="M72" s="3">
+      <c r="O72" s="3">
         <v>2695400</v>
       </c>
-      <c r="N72" s="3">
+      <c r="P72" s="3">
         <v>2613000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="Q72" s="3">
         <v>2562200</v>
       </c>
-      <c r="P72" s="3">
+      <c r="R72" s="3">
         <v>2469100</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="S72" s="3">
         <v>2326300</v>
       </c>
     </row>
-    <row r="73" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3517,8 +3871,14 @@
       <c r="Q73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R73" s="3">
+        <v>0</v>
+      </c>
+      <c r="S73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3564,8 +3924,14 @@
       <c r="Q74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R74" s="3">
+        <v>0</v>
+      </c>
+      <c r="S74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3611,55 +3977,67 @@
       <c r="Q75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R75" s="3">
+        <v>0</v>
+      </c>
+      <c r="S75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>3761500</v>
+      </c>
+      <c r="E76" s="3">
+        <v>3789100</v>
+      </c>
+      <c r="F76" s="3">
         <v>3971100</v>
       </c>
-      <c r="E76" s="3">
+      <c r="G76" s="3">
         <v>3949100</v>
       </c>
-      <c r="F76" s="3">
+      <c r="H76" s="3">
         <v>3704600</v>
       </c>
-      <c r="G76" s="3">
+      <c r="I76" s="3">
         <v>3333000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="J76" s="3">
         <v>3273400</v>
       </c>
-      <c r="I76" s="3">
+      <c r="K76" s="3">
         <v>3511600</v>
       </c>
-      <c r="J76" s="3">
+      <c r="L76" s="3">
         <v>3154700</v>
       </c>
-      <c r="K76" s="3">
+      <c r="M76" s="3">
         <v>3142600</v>
       </c>
-      <c r="L76" s="3">
+      <c r="N76" s="3">
         <v>3329300</v>
       </c>
-      <c r="M76" s="3">
+      <c r="O76" s="3">
         <v>3065600</v>
       </c>
-      <c r="N76" s="3">
+      <c r="P76" s="3">
         <v>3024000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="Q76" s="3">
         <v>2965200</v>
       </c>
-      <c r="P76" s="3">
+      <c r="R76" s="3">
         <v>2897200</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="S76" s="3">
         <v>2729700</v>
       </c>
     </row>
-    <row r="77" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3705,60 +4083,72 @@
       <c r="Q77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R77" s="3">
+        <v>0</v>
+      </c>
+      <c r="S77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:19" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E80" s="2">
+        <v>46112</v>
+      </c>
+      <c r="F80" s="2">
         <v>46022</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45930</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>45838</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>45747</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>45657</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>45565</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>45473</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>45382</v>
       </c>
-      <c r="L80" s="2">
+      <c r="N80" s="2">
         <v>45291</v>
       </c>
-      <c r="M80" s="2">
+      <c r="O80" s="2">
         <v>45199</v>
       </c>
-      <c r="N80" s="2">
+      <c r="P80" s="2">
         <v>45107</v>
       </c>
-      <c r="O80" s="2">
+      <c r="Q80" s="2">
         <v>45016</v>
       </c>
-      <c r="P80" s="2">
+      <c r="R80" s="2">
         <v>44926</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="S80" s="2">
         <v>44834</v>
       </c>
     </row>
-    <row r="81" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
@@ -3804,8 +4194,14 @@
       <c r="Q81" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="82" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R81" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S81" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="82" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3823,55 +4219,63 @@
       <c r="O82" s="3"/>
       <c r="P82" s="3"/>
       <c r="Q82" s="3"/>
-    </row>
-    <row r="83" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R82" s="3"/>
+      <c r="S82" s="3"/>
+    </row>
+    <row r="83" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>85900</v>
+      </c>
+      <c r="E83" s="3">
+        <v>77300</v>
+      </c>
+      <c r="F83" s="3">
         <v>74700</v>
       </c>
-      <c r="E83" s="3">
+      <c r="G83" s="3">
         <v>80100</v>
       </c>
-      <c r="F83" s="3">
+      <c r="H83" s="3">
         <v>73800</v>
       </c>
-      <c r="G83" s="3">
+      <c r="I83" s="3">
         <v>73600</v>
       </c>
-      <c r="H83" s="3">
+      <c r="J83" s="3">
         <v>79700</v>
       </c>
-      <c r="I83" s="3">
+      <c r="K83" s="3">
         <v>73400</v>
       </c>
-      <c r="J83" s="3">
+      <c r="L83" s="3">
         <v>73500</v>
       </c>
-      <c r="K83" s="3">
+      <c r="M83" s="3">
         <v>72100</v>
       </c>
-      <c r="L83" s="3">
+      <c r="N83" s="3">
         <v>75300</v>
       </c>
-      <c r="M83" s="3">
+      <c r="O83" s="3">
         <v>70900</v>
       </c>
-      <c r="N83" s="3">
+      <c r="P83" s="3">
         <v>68800</v>
       </c>
-      <c r="O83" s="3">
+      <c r="Q83" s="3">
         <v>71300</v>
       </c>
-      <c r="P83" s="3">
+      <c r="R83" s="3">
         <v>75000</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="S83" s="3">
         <v>73200</v>
       </c>
     </row>
-    <row r="84" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3917,8 +4321,14 @@
       <c r="Q84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R84" s="3">
+        <v>0</v>
+      </c>
+      <c r="S84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3964,8 +4374,14 @@
       <c r="Q85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R85" s="3">
+        <v>0</v>
+      </c>
+      <c r="S85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4011,8 +4427,14 @@
       <c r="Q86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R86" s="3">
+        <v>0</v>
+      </c>
+      <c r="S86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4058,8 +4480,14 @@
       <c r="Q87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R87" s="3">
+        <v>0</v>
+      </c>
+      <c r="S87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4105,55 +4533,67 @@
       <c r="Q88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R88" s="3">
+        <v>0</v>
+      </c>
+      <c r="S88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>200600</v>
+      </c>
+      <c r="E89" s="3">
+        <v>202100</v>
+      </c>
+      <c r="F89" s="3">
         <v>241300</v>
       </c>
-      <c r="E89" s="3">
+      <c r="G89" s="3">
         <v>239900</v>
       </c>
-      <c r="F89" s="3">
+      <c r="H89" s="3">
         <v>192300</v>
       </c>
-      <c r="G89" s="3">
+      <c r="I89" s="3">
         <v>173000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="J89" s="3">
         <v>202900</v>
       </c>
-      <c r="I89" s="3">
+      <c r="K89" s="3">
         <v>217600</v>
       </c>
-      <c r="J89" s="3">
+      <c r="L89" s="3">
         <v>152400</v>
       </c>
-      <c r="K89" s="3">
+      <c r="M89" s="3">
         <v>151800</v>
       </c>
-      <c r="L89" s="3">
+      <c r="N89" s="3">
         <v>216300</v>
       </c>
-      <c r="M89" s="3">
+      <c r="O89" s="3">
         <v>199200</v>
       </c>
-      <c r="N89" s="3">
+      <c r="P89" s="3">
         <v>176700</v>
       </c>
-      <c r="O89" s="3">
+      <c r="Q89" s="3">
         <v>173300</v>
       </c>
-      <c r="P89" s="3">
+      <c r="R89" s="3">
         <v>137300</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="S89" s="3">
         <v>129400</v>
       </c>
     </row>
-    <row r="90" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4171,55 +4611,63 @@
       <c r="O90" s="3"/>
       <c r="P90" s="3"/>
       <c r="Q90" s="3"/>
-    </row>
-    <row r="91" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R90" s="3"/>
+      <c r="S90" s="3"/>
+    </row>
+    <row r="91" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-161000</v>
+      </c>
+      <c r="E91" s="3">
+        <v>-162100</v>
+      </c>
+      <c r="F91" s="3">
         <v>-175200</v>
       </c>
-      <c r="E91" s="3">
+      <c r="G91" s="3">
         <v>-174300</v>
       </c>
-      <c r="F91" s="3">
+      <c r="H91" s="3">
         <v>-164200</v>
       </c>
-      <c r="G91" s="3">
+      <c r="I91" s="3">
         <v>-147700</v>
       </c>
-      <c r="H91" s="3">
+      <c r="J91" s="3">
         <v>-152500</v>
       </c>
-      <c r="I91" s="3">
+      <c r="K91" s="3">
         <v>-163500</v>
       </c>
-      <c r="J91" s="3">
+      <c r="L91" s="3">
         <v>-111300</v>
       </c>
-      <c r="K91" s="3">
+      <c r="M91" s="3">
         <v>-110900</v>
       </c>
-      <c r="L91" s="3">
+      <c r="N91" s="3">
         <v>-139100</v>
       </c>
-      <c r="M91" s="3">
+      <c r="O91" s="3">
         <v>-128000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="P91" s="3">
         <v>-82600</v>
       </c>
-      <c r="O91" s="3">
+      <c r="Q91" s="3">
         <v>-81000</v>
       </c>
-      <c r="P91" s="3">
+      <c r="R91" s="3">
         <v>-60500</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="S91" s="3">
         <v>-57000</v>
       </c>
     </row>
-    <row r="92" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4265,8 +4713,14 @@
       <c r="Q92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R92" s="3">
+        <v>0</v>
+      </c>
+      <c r="S92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4312,55 +4766,67 @@
       <c r="Q93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R93" s="3">
+        <v>0</v>
+      </c>
+      <c r="S93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-27000</v>
+      </c>
+      <c r="E94" s="3">
+        <v>-27200</v>
+      </c>
+      <c r="F94" s="3">
         <v>-325600</v>
       </c>
-      <c r="E94" s="3">
+      <c r="G94" s="3">
         <v>-323700</v>
       </c>
-      <c r="F94" s="3">
+      <c r="H94" s="3">
         <v>-258800</v>
       </c>
-      <c r="G94" s="3">
+      <c r="I94" s="3">
         <v>-232900</v>
       </c>
-      <c r="H94" s="3">
+      <c r="J94" s="3">
         <v>-171000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="K94" s="3">
         <v>-183500</v>
       </c>
-      <c r="J94" s="3">
+      <c r="L94" s="3">
         <v>-19000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="M94" s="3">
         <v>-18900</v>
       </c>
-      <c r="L94" s="3">
+      <c r="N94" s="3">
         <v>-208300</v>
       </c>
-      <c r="M94" s="3">
+      <c r="O94" s="3">
         <v>-191800</v>
       </c>
-      <c r="N94" s="3">
+      <c r="P94" s="3">
         <v>101000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="Q94" s="3">
         <v>99100</v>
       </c>
-      <c r="P94" s="3">
+      <c r="R94" s="3">
         <v>-179600</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="S94" s="3">
         <v>-169200</v>
       </c>
     </row>
-    <row r="95" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4378,55 +4844,63 @@
       <c r="O95" s="3"/>
       <c r="P95" s="3"/>
       <c r="Q95" s="3"/>
-    </row>
-    <row r="96" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R95" s="3"/>
+      <c r="S95" s="3"/>
+    </row>
+    <row r="96" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="D96" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="E96" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="F96" s="3">
+      <c r="D96" s="3">
+        <v>161500</v>
+      </c>
+      <c r="E96" s="3">
+        <v>162700</v>
+      </c>
+      <c r="F96" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G96" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H96" s="3">
         <v>110000</v>
       </c>
-      <c r="G96" s="3">
+      <c r="I96" s="3">
         <v>99000</v>
       </c>
-      <c r="H96" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="I96" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="J96" s="3">
+      <c r="J96" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="K96" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L96" s="3">
         <v>90500</v>
       </c>
-      <c r="K96" s="3">
+      <c r="M96" s="3">
         <v>90200</v>
       </c>
-      <c r="L96" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="M96" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="N96" s="3">
+      <c r="N96" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O96" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P96" s="3">
         <v>60100</v>
       </c>
-      <c r="O96" s="3">
+      <c r="Q96" s="3">
         <v>58900</v>
       </c>
-      <c r="P96" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Q96" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="97" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R96" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S96" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="97" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4472,8 +4946,14 @@
       <c r="Q97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R97" s="3">
+        <v>0</v>
+      </c>
+      <c r="S97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4519,8 +4999,14 @@
       <c r="Q98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R98" s="3">
+        <v>0</v>
+      </c>
+      <c r="S98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4566,145 +5052,169 @@
       <c r="Q99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R99" s="3">
+        <v>0</v>
+      </c>
+      <c r="S99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-153000</v>
+      </c>
+      <c r="E100" s="3">
+        <v>-154200</v>
+      </c>
+      <c r="F100" s="3">
         <v>20600</v>
       </c>
-      <c r="E100" s="3">
+      <c r="G100" s="3">
         <v>20500</v>
       </c>
-      <c r="F100" s="3">
+      <c r="H100" s="3">
         <v>27300</v>
       </c>
-      <c r="G100" s="3">
+      <c r="I100" s="3">
         <v>24500</v>
       </c>
-      <c r="H100" s="3">
+      <c r="J100" s="3">
         <v>21700</v>
       </c>
-      <c r="I100" s="3">
+      <c r="K100" s="3">
         <v>23300</v>
       </c>
-      <c r="J100" s="3">
+      <c r="L100" s="3">
         <v>-170500</v>
       </c>
-      <c r="K100" s="3">
+      <c r="M100" s="3">
         <v>-169900</v>
       </c>
-      <c r="L100" s="3">
+      <c r="N100" s="3">
         <v>28100</v>
       </c>
-      <c r="M100" s="3">
+      <c r="O100" s="3">
         <v>25900</v>
       </c>
-      <c r="N100" s="3">
+      <c r="P100" s="3">
         <v>-288500</v>
       </c>
-      <c r="O100" s="3">
+      <c r="Q100" s="3">
         <v>-282900</v>
       </c>
-      <c r="P100" s="3">
+      <c r="R100" s="3">
         <v>-28900</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="S100" s="3">
         <v>-27200</v>
       </c>
     </row>
-    <row r="101" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-2400</v>
+      </c>
+      <c r="E101" s="3">
+        <v>-2100</v>
+      </c>
+      <c r="F101" s="3">
         <v>-3500</v>
       </c>
-      <c r="E101" s="3">
+      <c r="G101" s="3">
         <v>-3700</v>
       </c>
-      <c r="F101" s="3">
+      <c r="H101" s="3">
         <v>-700</v>
       </c>
-      <c r="G101" s="3">
+      <c r="I101" s="3">
         <v>-700</v>
       </c>
-      <c r="H101" s="3">
+      <c r="J101" s="3">
         <v>-2200</v>
       </c>
-      <c r="I101" s="3">
+      <c r="K101" s="3">
         <v>-2000</v>
       </c>
-      <c r="J101" s="3">
+      <c r="L101" s="3">
         <v>800</v>
       </c>
-      <c r="K101" s="3">
+      <c r="M101" s="3">
         <v>800</v>
       </c>
-      <c r="L101" s="3">
+      <c r="N101" s="3">
         <v>200</v>
       </c>
-      <c r="M101" s="3">
+      <c r="O101" s="3">
         <v>200</v>
       </c>
-      <c r="N101" s="3">
+      <c r="P101" s="3">
         <v>400</v>
       </c>
-      <c r="O101" s="3">
+      <c r="Q101" s="3">
         <v>400</v>
       </c>
-      <c r="P101" s="3">
+      <c r="R101" s="3">
         <v>-1700</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="S101" s="3">
         <v>-1700</v>
       </c>
     </row>
-    <row r="102" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>23600</v>
+      </c>
+      <c r="E102" s="3">
+        <v>23800</v>
+      </c>
+      <c r="F102" s="3">
         <v>-61400</v>
       </c>
-      <c r="E102" s="3">
+      <c r="G102" s="3">
         <v>-61100</v>
       </c>
-      <c r="F102" s="3">
+      <c r="H102" s="3">
         <v>-41700</v>
       </c>
-      <c r="G102" s="3">
+      <c r="I102" s="3">
         <v>-37500</v>
       </c>
-      <c r="H102" s="3">
+      <c r="J102" s="3">
         <v>50000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="K102" s="3">
         <v>53700</v>
       </c>
-      <c r="J102" s="3">
+      <c r="L102" s="3">
         <v>-37800</v>
       </c>
-      <c r="K102" s="3">
+      <c r="M102" s="3">
         <v>-37600</v>
       </c>
-      <c r="L102" s="3">
+      <c r="N102" s="3">
         <v>33900</v>
       </c>
-      <c r="M102" s="3">
+      <c r="O102" s="3">
         <v>31200</v>
       </c>
-      <c r="N102" s="3">
+      <c r="P102" s="3">
         <v>-10000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="Q102" s="3">
         <v>-9800</v>
       </c>
-      <c r="P102" s="3">
+      <c r="R102" s="3">
         <v>-70900</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="S102" s="3">
         <v>-66800</v>
       </c>
     </row>
